--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.92971374796814</v>
+        <v>1.288578484044823</v>
       </c>
       <c r="D2" t="n">
-        <v>7.512430500922879</v>
+        <v>1.220769956399968</v>
       </c>
       <c r="E2" t="n">
-        <v>25.89834311353972</v>
+        <v>4.208480755950204</v>
       </c>
       <c r="F2" t="n">
-        <v>3.581670973254128</v>
+        <v>0.5820215331537958</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.896992529352318</v>
+        <v>1.283261286019752</v>
       </c>
       <c r="D3" t="n">
-        <v>6.388398759923555</v>
+        <v>1.038114798487578</v>
       </c>
       <c r="E3" t="n">
-        <v>25.89834311353972</v>
+        <v>4.208480755950204</v>
       </c>
       <c r="F3" t="n">
-        <v>3.581670973254128</v>
+        <v>0.5820215331537958</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.788186722657393</v>
+        <v>1.428080342431826</v>
       </c>
       <c r="D4" t="n">
-        <v>6.691303720435517</v>
+        <v>1.087336854570772</v>
       </c>
       <c r="E4" t="n">
-        <v>25.89834311353972</v>
+        <v>4.208480755950204</v>
       </c>
       <c r="F4" t="n">
-        <v>3.581670973254128</v>
+        <v>0.5820215331537958</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.76031127642397</v>
+        <v>2.561050582418896</v>
       </c>
       <c r="D5" t="n">
-        <v>15.40935550060987</v>
+        <v>2.504020268849103</v>
       </c>
       <c r="E5" t="n">
-        <v>25.89834311353972</v>
+        <v>4.208480755950204</v>
       </c>
       <c r="F5" t="n">
-        <v>3.581670973254128</v>
+        <v>0.5820215331537958</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>69.60012174548162</v>
+        <v>11.31001978364076</v>
       </c>
       <c r="D6" t="n">
-        <v>4.003470716488104</v>
+        <v>0.650563991429317</v>
       </c>
       <c r="E6" t="n">
-        <v>25.89834311353972</v>
+        <v>4.208480755950204</v>
       </c>
       <c r="F6" t="n">
-        <v>3.581670973254128</v>
+        <v>0.5820215331537958</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.11465713148277</v>
+        <v>9.606131783865949</v>
       </c>
       <c r="D7" t="n">
-        <v>6.636407107828759</v>
+        <v>1.078416155022173</v>
       </c>
       <c r="E7" t="n">
-        <v>25.89834311353972</v>
+        <v>4.208480755950204</v>
       </c>
       <c r="F7" t="n">
-        <v>3.581670973254128</v>
+        <v>0.5820215331537958</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
